--- a/data/trans_orig/IP1001-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,42 +773,42 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>3709</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>3097</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98634</t>
+          <t>98392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103726</t>
+          <t>103655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94448</t>
+          <t>93836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195013</t>
+          <t>194861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200842</t>
+          <t>200922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>10943</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6089</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>6073</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>11532</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79631</t>
+          <t>79448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>85782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>83742</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80091</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>85302</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>167286</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>162416</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>170104</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>83742</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>79881</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85309</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>167286</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>161827</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>170499</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61747</t>
+          <t>61960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>66853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87704</t>
+          <t>88541</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96557</t>
+          <t>96580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153343</t>
+          <t>152948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162429</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191238</t>
+          <t>192154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198680</t>
+          <t>199247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192779</t>
+          <t>192957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199809</t>
+          <t>199867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388113</t>
+          <t>388315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>397774</t>
+          <t>397619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94527</t>
+          <t>94125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101958</t>
+          <t>101686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119844</t>
+          <t>119730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125995</t>
+          <t>125992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216933</t>
+          <t>217650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226739</t>
+          <t>226817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69688</t>
+          <t>69255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69302</t>
+          <t>68761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>139874</t>
+          <t>140647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146626</t>
+          <t>146632</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28798</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48649</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>611878</t>
+          <t>611002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>625580</t>
+          <t>625725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>659256</t>
+          <t>658595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>672206</t>
+          <t>672667</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1274810</t>
+          <t>1274295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1294661</t>
+          <t>1294608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84996</t>
+          <t>85012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172643</t>
+          <t>172634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88526</t>
+          <t>88193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90257</t>
+          <t>90627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95500</t>
+          <t>96111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181261</t>
+          <t>181223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187774</t>
+          <t>187676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80804</t>
+          <t>80758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83194</t>
+          <t>83091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166080</t>
+          <t>166701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193615</t>
+          <t>192711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202282</t>
+          <t>202200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213791</t>
+          <t>213603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>222769</t>
+          <t>222805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411136</t>
+          <t>410736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>423453</t>
+          <t>423251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140463</t>
+          <t>140851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147844</t>
+          <t>147846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131238</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139092</t>
+          <t>138599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274612</t>
+          <t>275539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285195</t>
+          <t>285512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69169</t>
+          <t>69318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123255</t>
+          <t>123246</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40241</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>654019</t>
+          <t>654364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>666174</t>
+          <t>666350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>688604</t>
+          <t>688663</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>702335</t>
+          <t>702755</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1347957</t>
+          <t>1349743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1366653</t>
+          <t>1366872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78221</t>
+          <t>78264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82550</t>
+          <t>82551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92170</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98507</t>
+          <t>98489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172831</t>
+          <t>172897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180356</t>
+          <t>180440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105690</t>
+          <t>106001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111534</t>
+          <t>111544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211959</t>
+          <t>211596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217299</t>
+          <t>217281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67958</t>
+          <t>67846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>74183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>128335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135237</t>
+          <t>135350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215409</t>
+          <t>214841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222238</t>
+          <t>222201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202441</t>
+          <t>202187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209372</t>
+          <t>209252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>420112</t>
+          <t>420858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>429803</t>
+          <t>430259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126147</t>
+          <t>125634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134411</t>
+          <t>134570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133652</t>
+          <t>134550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141200</t>
+          <t>141515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263691</t>
+          <t>263158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274052</t>
+          <t>273829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55565</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60472</t>
+          <t>60489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121853</t>
+          <t>121572</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127714</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25389</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648832</t>
+          <t>649994</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>662283</t>
+          <t>662596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>682693</t>
+          <t>682874</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>696985</t>
+          <t>696892</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1337615</t>
+          <t>1336781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1355850</t>
+          <t>1355767</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96587</t>
+          <t>95883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103082</t>
+          <t>103000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115813</t>
+          <t>120910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221012</t>
+          <t>220562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238245</t>
+          <t>238292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88129</t>
+          <t>87234</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94089</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85360</t>
+          <t>84331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94510</t>
+          <t>94048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176310</t>
+          <t>176776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187411</t>
+          <t>187437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47959</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61237</t>
+          <t>60925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111146</t>
+          <t>110720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16399</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>23070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207293</t>
+          <t>207036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216013</t>
+          <t>215895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201873</t>
+          <t>202590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213308</t>
+          <t>213503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414562</t>
+          <t>413212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>428088</t>
+          <t>427597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114044</t>
+          <t>114175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153552</t>
+          <t>152474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161066</t>
+          <t>160992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270729</t>
+          <t>270706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279333</t>
+          <t>279541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66462</t>
+          <t>66666</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62060</t>
+          <t>61683</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70499</t>
+          <t>70303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130760</t>
+          <t>130206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139024</t>
+          <t>139219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>41044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57866</t>
+          <t>55653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635447</t>
+          <t>634978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648500</t>
+          <t>648764</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>707637</t>
+          <t>708181</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>730572</t>
+          <t>730959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1348697</t>
+          <t>1350910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1375744</t>
+          <t>1376107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
